--- a/output/pdf_financials_xlsx/LUC.xlsx
+++ b/output/pdf_financials_xlsx/LUC.xlsx
@@ -984,22 +984,22 @@
         </is>
       </c>
       <c r="M9" s="3" t="n">
-        <v>0</v>
+        <v>13.511</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>0</v>
+        <v>24.871</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>0</v>
+        <v>24.101</v>
       </c>
       <c r="P9" s="3" t="n">
-        <v>0</v>
+        <v>20.056</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>0</v>
+        <v>23.208</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>0</v>
+        <v>17.737</v>
       </c>
     </row>
     <row r="10">
@@ -1459,7 +1459,7 @@
         <v>12.809199</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>18.673892</v>
+        <v>-18.673892</v>
       </c>
       <c r="E16" s="1" t="inlineStr">
         <is>
@@ -1527,10 +1527,10 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>-0</v>
+        <v>-3.47787</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>2.822033</v>
+        <v>-28.440431</v>
       </c>
       <c r="D17" s="3" t="n">
         <v>-0</v>
@@ -1785,13 +1785,13 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>1.738935</v>
+        <v>-1.738935</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>15.631232</v>
+        <v>-15.631232</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>18.673892</v>
+        <v>-18.673892</v>
       </c>
       <c r="E20" s="1" t="inlineStr">
         <is>
@@ -2007,13 +2007,13 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>1.738935</v>
+        <v>-1.738935</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>15.631232</v>
+        <v>-15.631232</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>18.673892</v>
+        <v>-18.673892</v>
       </c>
       <c r="E23" s="1" t="inlineStr">
         <is>
@@ -2262,10 +2262,10 @@
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>260.520533</v>
+        <v>-260.520533</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>373.47784</v>
+        <v>-373.47784</v>
       </c>
       <c r="E26" s="1" t="inlineStr">
         <is>
@@ -2343,7 +2343,7 @@
         <v>13.263949</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>19.6372</v>
+        <v>-17.710584</v>
       </c>
       <c r="E27" s="1" t="inlineStr">
         <is>
@@ -2491,7 +2491,7 @@
         <v>14.659764</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>22.278643</v>
+        <v>-15.069141</v>
       </c>
       <c r="E29" s="1" t="inlineStr">
         <is>
@@ -2639,13 +2639,13 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>22.03129953715295</v>
+        <v>222.031299537153</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E31" s="1" t="inlineStr">
         <is>
@@ -6965,7 +6965,7 @@
         </is>
       </c>
       <c r="B99" s="3" t="n">
-        <v>1.738935</v>
+        <v>-1.738935</v>
       </c>
       <c r="C99" s="3" t="n">
         <v>-15.631232</v>
@@ -40994,7 +40994,11 @@
           <t>Royalty expenses (Note 13)</t>
         </is>
       </c>
-      <c r="D315" t="inlineStr"/>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
       <c r="E315" t="inlineStr">
         <is>
           <t>-</t>
@@ -45225,7 +45229,11 @@
           <t>Royalty expenses (Note 8)</t>
         </is>
       </c>
-      <c r="D358" t="inlineStr"/>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
       <c r="E358" t="inlineStr">
         <is>
           <t>-</t>
@@ -48907,10 +48915,10 @@
         </is>
       </c>
       <c r="F395" s="5" t="n">
-        <v>15.631232</v>
+        <v>-15.631232</v>
       </c>
       <c r="G395" s="5" t="n">
-        <v>18.673892</v>
+        <v>-18.673892</v>
       </c>
       <c r="H395" t="inlineStr">
         <is>
@@ -51031,10 +51039,10 @@
         </is>
       </c>
       <c r="E416" s="5" t="n">
-        <v>1.738935</v>
+        <v>-1.738935</v>
       </c>
       <c r="F416" s="5" t="n">
-        <v>12.809199</v>
+        <v>-12.809199</v>
       </c>
       <c r="G416" t="inlineStr">
         <is>
@@ -51641,10 +51649,10 @@
         </is>
       </c>
       <c r="E422" s="5" t="n">
-        <v>1.738935</v>
+        <v>-1.738935</v>
       </c>
       <c r="F422" s="5" t="n">
-        <v>12.809199</v>
+        <v>-12.809199</v>
       </c>
       <c r="G422" t="inlineStr">
         <is>
@@ -52041,10 +52049,10 @@
         </is>
       </c>
       <c r="E426" s="5" t="n">
-        <v>2.14423</v>
+        <v>-2.14423</v>
       </c>
       <c r="F426" s="5" t="n">
-        <v>12.1044</v>
+        <v>-12.1044</v>
       </c>
       <c r="G426" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/LUC.xlsx
+++ b/output/pdf_financials_xlsx/LUC.xlsx
@@ -2809,7 +2809,7 @@
         <v>48.589409</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>13.261484</v>
+        <v>13.261</v>
       </c>
       <c r="F34" s="3" t="n">
         <v>49.364</v>
@@ -2854,7 +2854,7 @@
         </is>
       </c>
       <c r="R34" s="3" t="n">
-        <v>0</v>
+        <v>22.788</v>
       </c>
     </row>
     <row r="35">
@@ -2937,7 +2937,7 @@
         <v>48.589409</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>13.261484</v>
+        <v>13.261</v>
       </c>
       <c r="F36" s="3" t="n">
         <v>49.364</v>
@@ -2982,7 +2982,7 @@
         </is>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0</v>
+        <v>22.788</v>
       </c>
     </row>
     <row r="37">
@@ -3705,7 +3705,7 @@
         <v>6.407282</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>5.612516</v>
+        <v>5.613</v>
       </c>
       <c r="F48" s="3" t="n">
         <v>3.683</v>
@@ -3750,7 +3750,7 @@
         </is>
       </c>
       <c r="R48" s="3" t="n">
-        <v>57.916</v>
+        <v>35.128</v>
       </c>
     </row>
     <row r="49">
@@ -8868,22 +8868,22 @@
         </is>
       </c>
       <c r="M124" s="3" t="n">
-        <v>0</v>
+        <v>-1.121</v>
       </c>
       <c r="N124" s="3" t="n">
-        <v>0</v>
+        <v>-0.9360000000000001</v>
       </c>
       <c r="O124" s="3" t="n">
-        <v>0</v>
+        <v>-3.055</v>
       </c>
       <c r="P124" s="3" t="n">
-        <v>0</v>
+        <v>-1.54</v>
       </c>
       <c r="Q124" s="3" t="n">
-        <v>0</v>
+        <v>-1.59</v>
       </c>
       <c r="R124" s="3" t="n">
-        <v>0</v>
+        <v>-1.891</v>
       </c>
     </row>
     <row r="125">
@@ -8942,22 +8942,22 @@
         </is>
       </c>
       <c r="M125" s="3" t="n">
-        <v>0</v>
+        <v>-1.121</v>
       </c>
       <c r="N125" s="3" t="n">
-        <v>0</v>
+        <v>-0.9360000000000001</v>
       </c>
       <c r="O125" s="3" t="n">
-        <v>0</v>
+        <v>-3.055</v>
       </c>
       <c r="P125" s="3" t="n">
-        <v>0</v>
+        <v>-1.54</v>
       </c>
       <c r="Q125" s="3" t="n">
-        <v>0</v>
+        <v>-1.59</v>
       </c>
       <c r="R125" s="3" t="n">
-        <v>0</v>
+        <v>-1.891</v>
       </c>
     </row>
     <row r="126">
@@ -9968,7 +9968,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -19744,7 +19744,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -27277,7 +27277,11 @@
           <t>Lease payments</t>
         </is>
       </c>
-      <c r="D178" t="inlineStr"/>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E178" t="inlineStr">
         <is>
           <t>-</t>
